--- a/proposal/创智汇30场活动方案排期表-WAIC对齐.xlsx
+++ b/proposal/创智汇30场活动方案排期表-WAIC对齐.xlsx
@@ -471,7 +471,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -590,7 +590,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -2361,7 +2361,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -3723,7 +3723,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -3844,7 +3844,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
@@ -4081,7 +4081,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -4253,7 +4253,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
@@ -4466,7 +4466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
